--- a/track2/methods_description_track2.xlsx
+++ b/track2/methods_description_track2.xlsx
@@ -852,7 +852,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>About 75–120 hours in total across both tracks, by one person working with an AI coding assistant, over August–October 2026 (an estimate: time was not formally tracked). This includes the Track 1 independent re-verification, the Track 2 analyses, the verification passes, the report and the video. No paid compute: every analysis ran on a dual-core laptop (i7-6500U, 11.8 GB RAM); most wall-clock time was API latency.</t>
+          <t>About 75–100 hours in total across both tracks, by one person working with an AI coding assistant, over August–October 2026 (an estimate: time was not formally tracked). This includes the Track 1 independent re-verification, the Track 2 analyses, the verification passes, the report and the video. Most of this time went into designing, checking and writing; re-running the scripted analyses does not require it. No paid compute: every analysis ran on a dual-core laptop (i7-6500U, 11.8 GB RAM); most wall-clock time was API latency.</t>
         </is>
       </c>
     </row>
